--- a/examples/addin.xlsx
+++ b/examples/addin.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026.10.0</t>
+          <t>2026.10.1</t>
         </is>
       </c>
     </row>
